--- a/samples/review_stats_demo_japanese/review_cases/CASE-003/レビュー結果記録表.xlsx
+++ b/samples/review_stats_demo_japanese/review_cases/CASE-003/レビュー結果記録表.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="内部仕様書" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="コード" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="テスト仕様書" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="リリース後" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -548,8 +549,9 @@
           <t>流出不良件数</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>2</v>
+      <c r="B11">
+        <f>COUNTIFS('リリース後'!J:J,"不良",'リリース後'!K:K,"対象")+COUNTIFS('リリース後'!J:J,"不良",'リリース後'!K:K,"")</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1003,7 +1005,7 @@
       <formula1>"対象,除外"</formula1>
     </dataValidation>
     <dataValidation sqref="L13:L100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"外部仕様書,内部仕様書,コード,テスト仕様書,後工程,リリース後"</formula1>
+      <formula1>"外部仕様書,内部仕様書,コード,テスト仕様書,リリース後,後工程"</formula1>
     </dataValidation>
     <dataValidation sqref="M13:M100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"外部仕様書,内部仕様書,コード,テスト仕様書,不明"</formula1>
@@ -1334,7 +1336,7 @@
       <formula1>"対象,除外"</formula1>
     </dataValidation>
     <dataValidation sqref="L13:L100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"外部仕様書,内部仕様書,コード,テスト仕様書,後工程,リリース後"</formula1>
+      <formula1>"外部仕様書,内部仕様書,コード,テスト仕様書,リリース後,後工程"</formula1>
     </dataValidation>
     <dataValidation sqref="M13:M100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"外部仕様書,内部仕様書,コード,テスト仕様書,不明"</formula1>
@@ -1726,7 +1728,7 @@
       <formula1>"対象,除外"</formula1>
     </dataValidation>
     <dataValidation sqref="L13:L100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"外部仕様書,内部仕様書,コード,テスト仕様書,後工程,リリース後"</formula1>
+      <formula1>"外部仕様書,内部仕様書,コード,テスト仕様書,リリース後,後工程"</formula1>
     </dataValidation>
     <dataValidation sqref="M13:M100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"外部仕様書,内部仕様書,コード,テスト仕様書,不明"</formula1>
@@ -1742,7 +1744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2109,128 +2111,6 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>リリース後障害</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>改行を含むCSVが取込先で分割された</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>対応済</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>品質管理B</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>レビューリーダー甲</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>不良</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>対象</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>リリース後</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>コード</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>後工程試験</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>文字コード変換エラーの再実行手順が不足</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>対応済</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>品質管理B</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>レビューリーダー甲</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>不良</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>対象</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>後工程</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>内部仕様書</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="J13:J100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -2240,7 +2120,399 @@
       <formula1>"対象,除外"</formula1>
     </dataValidation>
     <dataValidation sqref="L13:L100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"外部仕様書,内部仕様書,コード,テスト仕様書,後工程,リリース後"</formula1>
+      <formula1>"外部仕様書,内部仕様書,コード,テスト仕様書,リリース後,後工程"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M13:M100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"外部仕様書,内部仕様書,コード,テスト仕様書,不明"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>レビュー者観点チェックリスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>状況</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>確認日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>リリース後の整合性を確認</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>リリース後の変更範囲を確認</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>共通チェックリスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>作業者確認日時</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>レビュー者確認日時</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>状況</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>成果物の版数と更新日が一致している</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>レビュー指摘の対応方針が記録されている</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>指摘項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>重大度</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>指摘箇所</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>指摘内容</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>対応日時</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>状況</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t>作業担当者</t>
+        </is>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>レビュー担当者</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>指摘分類</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr">
+        <is>
+          <t>指標対象</t>
+        </is>
+      </c>
+      <c r="L12" s="1" t="inlineStr">
+        <is>
+          <t>検出工程</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="inlineStr">
+        <is>
+          <t>原因工程</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>リリース後障害</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>改行を含むCSVが取込先で分割された</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>品質管理B</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>レビューリーダー乙</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>不良</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>リリース後</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>コード</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>後工程試験</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>文字コード変換エラーの再実行手順が不足</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>品質管理B</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>レビューリーダー乙</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>不良</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>後工程</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>内部仕様書</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation sqref="J13:J100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"不良,改善,軽微,質問,対象外"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K13:K100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"対象,除外"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L13:L100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"外部仕様書,内部仕様書,コード,テスト仕様書,リリース後,後工程"</formula1>
     </dataValidation>
     <dataValidation sqref="M13:M100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"外部仕様書,内部仕様書,コード,テスト仕様書,不明"</formula1>
